--- a/diseases/d183/2010-2014.xlsx
+++ b/diseases/d183/2010-2014.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -913,9 +910,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1061,9 +1055,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1209,9 +1200,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1357,9 +1345,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1505,9 +1490,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1653,9 +1635,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -1801,9 +1780,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -1949,9 +1925,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2097,9 +2070,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2245,9 +2215,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -2393,9 +2360,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -2541,9 +2505,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -2689,9 +2650,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -2837,9 +2795,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -2985,9 +2940,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3133,9 +3085,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -3281,9 +3230,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -3429,9 +3375,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -3577,9 +3520,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -3725,9 +3665,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -3873,9 +3810,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4021,9 +3955,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -4169,9 +4100,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -4317,9 +4245,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -4465,9 +4390,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -4613,9 +4535,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -4761,9 +4680,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -4909,9 +4825,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -5057,9 +4970,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -5205,9 +5115,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -5353,9 +5260,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -5501,9 +5405,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -6093,9 +5994,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -6833,9 +6731,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -7721,9 +7616,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -8461,9 +8353,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -9349,9 +9238,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -10089,9 +9975,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -10829,9 +10712,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -11569,9 +11449,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -12457,9 +12334,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -13197,9 +13071,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -13937,9 +13808,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -14825,9 +14693,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -15565,9 +15430,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -16453,9 +16315,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -17193,9 +17052,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -17933,9 +17789,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -18821,9 +18674,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -19561,9 +19411,6 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -20301,9 +20148,6 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0</v>
       </c>
@@ -21041,9 +20885,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -21929,9 +21770,6 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0</v>
       </c>
@@ -22669,9 +22507,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
@@ -23557,9 +23392,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
@@ -24297,9 +24129,6 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0</v>
       </c>
@@ -25037,9 +24866,6 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
@@ -25925,9 +25751,6 @@
       <c r="O172" t="n">
         <v>0</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0</v>
       </c>
@@ -26663,9 +26486,6 @@
         <v>0</v>
       </c>
       <c r="O177" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q177" t="n">
         <v>0</v>
       </c>
       <c r="R177" t="n">
